--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487593_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487593_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5616</v>
+        <v>10.6072</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2298</v>
+        <v>10.9295</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3318</v>
+        <v>-0.3223</v>
       </c>
       <c r="G2" t="n">
         <v>5.6329</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4302</v>
+        <v>0.4758</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2445</v>
+        <v>-0.0558</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1858</v>
+        <v>0.5317</v>
       </c>
       <c r="V2" t="n">
         <v>3.5283</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9278</v>
+        <v>4.0542</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8205</v>
+        <v>3.9196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1073</v>
+        <v>0.1346</v>
       </c>
       <c r="G3" t="n">
         <v>0.053</v>
@@ -688,13 +688,13 @@
         <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3405</v>
+        <v>0.4669</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2146</v>
+        <v>0.3137</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1259</v>
+        <v>0.1531</v>
       </c>
       <c r="V3" t="n">
         <v>1.788</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8773</v>
+        <v>1.0319</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4246</v>
+        <v>1.5247</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5473</v>
+        <v>-0.4927</v>
       </c>
       <c r="G4" t="n">
         <v>0.4211</v>
@@ -766,13 +766,13 @@
         <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1095</v>
+        <v>0.0451</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0722</v>
+        <v>0.1267</v>
       </c>
       <c r="V4" t="n">
         <v>-0.4045</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3398</v>
+        <v>0.2669</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7476</v>
+        <v>0.6475</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4078</v>
+        <v>-0.3805</v>
       </c>
       <c r="G5" t="n">
         <v>1.4687</v>
@@ -844,13 +844,13 @@
         <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9637</v>
+        <v>0.8908</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6684</v>
+        <v>0.5683</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2952</v>
+        <v>0.3225</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7343</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1378</v>
+        <v>0.2354</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1205</v>
+        <v>0.2799</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0173</v>
+        <v>-0.0445</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4953</v>
@@ -922,13 +922,13 @@
         <v>0.3881</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0305</v>
+        <v>0.3426</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1817</v>
+        <v>0.2187</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1512</v>
+        <v>0.1239</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. RODRÍGUEZ MACHÍN</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1395</v>
+        <v>-0.2708</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2225</v>
+        <v>-0.6011</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.362</v>
+        <v>0.3303</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5598</v>
+        <v>0.7299</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2645</v>
+        <v>0.5965</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2953</v>
+        <v>0.1335</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2036</v>
+        <v>0.3295</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3254</v>
+        <v>0.3295</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1218</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3561</v>
+        <v>0.4004</v>
       </c>
       <c r="N7" t="n">
-        <v>0.061</v>
+        <v>0.2669</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4171</v>
+        <v>0.1335</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4024</v>
+        <v>0.2515</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3665</v>
+        <v>0.0395</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0359</v>
+        <v>0.212</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.788</v>
+        <v>-0.2821</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.0119</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>I. REBERGEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3164</v>
+        <v>-0.3672</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7012</v>
+        <v>-1.4124</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3848</v>
+        <v>1.0453</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7299</v>
+        <v>0.7961</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5965</v>
+        <v>2.2936</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1335</v>
+        <v>-1.4976</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3295</v>
+        <v>1.543</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3295</v>
+        <v>2.3398</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.7968</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4004</v>
+        <v>-0.7469</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2669</v>
+        <v>-0.0462</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1335</v>
+        <v>-0.7008</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9702</v>
+        <v>-3.1045</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-5.0448</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2059</v>
+        <v>0.5577</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0606</v>
+        <v>0.3014</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2665</v>
+        <v>0.2563</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2821</v>
+        <v>1.3836</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2821</v>
+        <v>-0.4045</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. REBERGEN</t>
+          <t>D. OJEDA DAVILA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8583</v>
+        <v>-1.0548</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7127</v>
+        <v>-3.7342</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8545</v>
+        <v>2.6794</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7961</v>
+        <v>-0.5583</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2936</v>
+        <v>0.6657</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4976</v>
+        <v>-1.224</v>
       </c>
       <c r="J9" t="n">
-        <v>1.543</v>
+        <v>-1.3859</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3398</v>
+        <v>0.4943</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7968</v>
+        <v>-1.8802</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7469</v>
+        <v>0.8275</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0462</v>
+        <v>0.1714</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7008</v>
+        <v>0.6562</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.1045</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.0448</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9403</v>
+        <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0244</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0011</v>
+        <v>-0.408</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0655</v>
+        <v>0.4324</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3836</v>
+        <v>0.2552</v>
       </c>
       <c r="W9" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4045</v>
+        <v>0.2552</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. OJEDA DAVILA</t>
+          <t>Y. RODRÍGUEZ MACHÍN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6916</v>
+        <v>-1.6409</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2347</v>
+        <v>0.7211</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5431</v>
+        <v>-2.362</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5583</v>
+        <v>-0.5598</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6657</v>
+        <v>-0.2645</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.224</v>
+        <v>-0.2953</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3859</v>
+        <v>-0.2036</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4943</v>
+        <v>-0.3254</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8802</v>
+        <v>0.1218</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8275</v>
+        <v>-0.3561</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1714</v>
+        <v>0.061</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6562</v>
+        <v>-0.4171</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7761</v>
+        <v>-0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.9009</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9085</v>
+        <v>0.865</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2961</v>
+        <v>0.0359</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2552</v>
+        <v>-1.788</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2552</v>
+        <v>-3.0119</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6642</v>
+        <v>-1.6999</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5753</v>
+        <v>-1.7745</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.0746</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5433</v>
@@ -1312,13 +1312,13 @@
         <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.897</v>
+        <v>0.0673</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6057</v>
+        <v>0.1951</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2914</v>
+        <v>-0.1278</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6938</v>
+        <v>-2.9569</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4211</v>
+        <v>-1.8205</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2727</v>
+        <v>-1.1364</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1563</v>
@@ -1390,13 +1390,13 @@
         <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8793</v>
+        <v>-0.1424</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9085</v>
+        <v>-0.3079</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0292</v>
+        <v>0.1655</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2403</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.204900000000002</v>
+        <v>8.205100000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>8.679500000000001</v>
+        <v>8.679600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4745000000000001</v>
+        <v>-0.4742000000000008</v>
       </c>
       <c r="G13" t="n">
         <v>3.7887</v>
@@ -1444,19 +1444,19 @@
         <v>11.4193</v>
       </c>
       <c r="K13" t="n">
-        <v>7.8598</v>
+        <v>7.859799999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>3.559399999999999</v>
+        <v>3.5594</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.630599999999999</v>
+        <v>-7.630599999999998</v>
       </c>
       <c r="N13" t="n">
         <v>0.01629999999999998</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.647000000000001</v>
+        <v>-7.646999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-0.9699999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>13.5824</v>
       </c>
       <c r="S13" t="n">
-        <v>3.880599999999999</v>
+        <v>3.880600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.648399999999999</v>
+        <v>1.6484</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2321</v>
+        <v>2.2322</v>
       </c>
       <c r="V13" t="n">
         <v>1.5059</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0549</v>
+        <v>1.8631</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1726</v>
+        <v>1.1716</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8823</v>
+        <v>0.6915</v>
       </c>
       <c r="G14" t="n">
         <v>3.4333</v>
@@ -1546,13 +1546,13 @@
         <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3768</v>
+        <v>0.1851</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0935</v>
+        <v>0.0925</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2833</v>
+        <v>0.0926</v>
       </c>
       <c r="V14" t="n">
         <v>-1.3672</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1516</v>
+        <v>0.4278</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2.2569</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1516</v>
+        <v>-1.8291</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1335</v>
+        <v>-0.8783</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-1.8982</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1335</v>
+        <v>1.02</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.9833</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.1236</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.8597</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1335</v>
+        <v>-2.8616</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-2.0218</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1335</v>
+        <v>-0.8398</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0182</v>
+        <v>-0.9761</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.2622</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0182</v>
+        <v>-0.7139</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>A. JIMÉNEZ BARRETO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1369</v>
+        <v>0.3741</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1568</v>
+        <v>4.1266</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0199</v>
+        <v>-3.7526</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8783</v>
+        <v>0.6279</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8982</v>
+        <v>-1.7845</v>
       </c>
       <c r="I16" t="n">
-        <v>1.02</v>
+        <v>2.4125</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9833</v>
+        <v>3.278</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1236</v>
+        <v>0.1648</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8597</v>
+        <v>3.1132</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8616</v>
+        <v>-2.65</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0218</v>
+        <v>-1.9493</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8398</v>
+        <v>-0.7008</v>
       </c>
       <c r="P16" t="n">
         <v>0.7761</v>
@@ -1702,28 +1702,28 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2669</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3623</v>
+        <v>-0.911</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9046</v>
+        <v>0.2109</v>
       </c>
       <c r="V16" t="n">
-        <v>1.506</v>
+        <v>-0.3299</v>
       </c>
       <c r="W16" t="n">
-        <v>1.506</v>
+        <v>2.7298</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-3.0597</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. JIMÉNEZ BARRETO</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0898</v>
+        <v>0.2928</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8263</v>
+        <v>2.5957</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.9161</v>
+        <v>-2.3029</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6279</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7845</v>
+        <v>-0.2175</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4125</v>
+        <v>0.9327</v>
       </c>
       <c r="J17" t="n">
-        <v>3.278</v>
+        <v>3.4987</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1648</v>
+        <v>1.5983</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1132</v>
+        <v>1.9003</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.65</v>
+        <v>-2.7835</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9493</v>
+        <v>-1.8158</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7008</v>
+        <v>-0.9677</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7761</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.164</v>
+        <v>-0.8701</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2113</v>
+        <v>-0.4686</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0474</v>
+        <v>-0.4015</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3299</v>
+        <v>1.2239</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7298</v>
+        <v>1.506</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.0597</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4257</v>
+        <v>0.1789</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0952</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5209</v>
+        <v>0.1789</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.1335</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9327</v>
+        <v>0.1335</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4987</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5983</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9003</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7835</v>
+        <v>0.1335</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8158</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9677</v>
+        <v>0.1335</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5886</v>
+        <v>0.0454</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9691</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6195000000000001</v>
+        <v>0.0454</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ABRIL RAMIRO</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6067</v>
+        <v>-0.9316</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2153</v>
+        <v>-0.6672</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6086</v>
+        <v>-0.2643</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.237</v>
+        <v>-0.8875</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2274</v>
+        <v>-0.2958</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4643</v>
+        <v>-0.5917</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.853</v>
+        <v>1.0112</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2719</v>
+        <v>0.9022</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="M19" t="n">
-        <v>0.616</v>
+        <v>-1.8987</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4992</v>
+        <v>-1.1979</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1168</v>
+        <v>-0.7008</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3284</v>
+        <v>2.1344</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0123</v>
+        <v>-1.3038</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6079</v>
+        <v>-0.7083</v>
       </c>
       <c r="U19" t="n">
         <v>-0.5955</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7403</v>
+        <v>0.0955</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7403</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>J. ABRIL RAMIRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1318</v>
+        <v>-1.0071</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-1.6157</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2643</v>
+        <v>0.6086</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8875</v>
+        <v>-0.237</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2958</v>
+        <v>0.2274</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5917</v>
+        <v>-0.4643</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0112</v>
+        <v>-0.853</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9022</v>
+        <v>-0.2719</v>
       </c>
       <c r="L20" t="n">
-        <v>0.109</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8987</v>
+        <v>0.616</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1979</v>
+        <v>0.4992</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7008</v>
+        <v>0.1168</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1344</v>
+        <v>2.3284</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.504</v>
+        <v>-0.3881</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9085</v>
+        <v>0.2075</v>
       </c>
       <c r="U20" t="n">
         <v>-0.5955</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0955</v>
+        <v>-1.7403</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0955</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.925</v>
+        <v>-3.4979</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2625</v>
+        <v>-1.5628</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6625</v>
+        <v>-1.935</v>
       </c>
       <c r="G21" t="n">
         <v>-3.3008</v>
@@ -2092,13 +2092,13 @@
         <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5698</v>
+        <v>-0.0031</v>
       </c>
       <c r="T21" t="n">
-        <v>0.305</v>
+        <v>0.0047</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2647</v>
+        <v>-0.0078</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3697</v>
+        <v>-5.9053</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.4314</v>
+        <v>-5.8308</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0617</v>
+        <v>-0.0745</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3951</v>
@@ -2170,13 +2170,13 @@
         <v>2.1344</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3342</v>
+        <v>0.1301</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7874</v>
+        <v>-0.1868</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4531</v>
+        <v>0.3169</v>
       </c>
       <c r="V22" t="n">
         <v>-0.894</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.205299999999999</v>
+        <v>-8.2052</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4742999999999995</v>
+        <v>0.4743000000000004</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.679499999999999</v>
+        <v>-8.679400000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.788799999999999</v>
+        <v>-3.7888</v>
       </c>
       <c r="H23" t="n">
         <v>-7.876300000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>4.0877</v>
+        <v>4.087700000000001</v>
       </c>
       <c r="J23" t="n">
         <v>7.630600000000001</v>
@@ -2248,7 +2248,7 @@
         <v>14.5526</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.8806</v>
+        <v>-3.8807</v>
       </c>
       <c r="T23" t="n">
         <v>-2.2322</v>
